--- a/output/pdf_financials_xlsx/ESXR.xlsx
+++ b/output/pdf_financials_xlsx/ESXR.xlsx
@@ -1656,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="93">
@@ -2562,7 +2562,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ESXR.xlsx
+++ b/output/pdf_financials_xlsx/ESXR.xlsx
@@ -891,10 +891,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.10493</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.265253</v>
       </c>
     </row>
     <row r="35">
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.10493</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.265253</v>
       </c>
     </row>
     <row r="37">
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.10493</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.265253</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/ESXR.xlsx
+++ b/output/pdf_financials_xlsx/ESXR.xlsx
@@ -643,10 +643,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.038147</v>
+        <v>-0.055147</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-0.094167</v>
+        <v>-0.077167</v>
       </c>
     </row>
     <row r="17">
@@ -656,10 +656,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>0.017</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.017</v>
       </c>
     </row>
     <row r="18">
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.038147</v>
+        <v>-0.055147</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.094167</v>
+        <v>-0.077167</v>
       </c>
     </row>
     <row r="28">
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.038147</v>
+        <v>-0.055147</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.094167</v>
+        <v>-0.077167</v>
       </c>
     </row>
     <row r="30">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-30.82669954847952</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-22.03014241839128</v>
       </c>
     </row>
     <row r="32">
@@ -2990,7 +2990,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
         <v>0.20475</v>
       </c>
@@ -3492,7 +3496,11 @@
           <t>Income tax recovery (expense) 10</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E47" s="5" t="n">
         <v>-0.017</v>
       </c>
